--- a/USBR24moLakeMead.xlsx
+++ b/USBR24moLakeMead.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fager\Box\LakeMeadAnalysis\LakeMead\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82E53F0-ADCA-4003-9404-84E279EDF5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{209420C7-C742-48B6-AB1F-4450424813A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="728" firstSheet="1" activeTab="5" xr2:uid="{C313E006-2F6C-4FB8-9F0B-34C8302D38CE}"/>
   </bookViews>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4874" uniqueCount="990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4877" uniqueCount="993">
   <si>
     <t>Date</t>
   </si>
@@ -3043,19 +3043,28 @@
     <t>USBR 24 Month Most Probable</t>
   </si>
   <si>
-    <t>Powell inflow</t>
-  </si>
-  <si>
     <t>Glen Canyon Dam Release</t>
   </si>
   <si>
-    <t>USBR Probable Minimums</t>
-  </si>
-  <si>
-    <t>Trace 1</t>
-  </si>
-  <si>
-    <t>Trace 2</t>
+    <t>Lowest calculated trace</t>
+  </si>
+  <si>
+    <t>Second lowest calcualted trace</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>Immersive Model Scenario 1</t>
+  </si>
+  <si>
+    <t>Immersive Model Scenario 2</t>
+  </si>
+  <si>
+    <t>USBR Probable Minimum for Lake Mead</t>
+  </si>
+  <si>
+    <t>Unregulated Inflow into Lake Powell</t>
   </si>
 </sst>
 </file>
@@ -3556,7 +3565,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>USBR Probable Minimums</c:v>
+                  <c:v>USBR Probable Minimum for Lake Mead</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3692,7 +3701,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Powell inflow</c:v>
+                  <c:v>Unregulated Inflow into Lake Powell</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3760,7 +3769,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Trace 1</c:v>
+                  <c:v>Immersive Model Scenario 1</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3828,7 +3837,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Trace 2</c:v>
+                  <c:v>Immersive Model Scenario 2</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4649,16 +4658,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>129540</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>541020</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:rowOff>99060</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>365760</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>167640</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -52013,7 +52022,7 @@
     <col min="2" max="2" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>625</v>
       </c>
@@ -52026,10 +52035,13 @@
       <c r="D1" t="s">
         <v>633</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="B2">
         <v>8.0039999999999996</v>
@@ -52041,7 +52053,7 @@
         <v>7.7160000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>984</v>
       </c>
@@ -52055,9 +52067,9 @@
         <v>7.9269999999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B4" s="8">
         <v>7.4809999999999999</v>
@@ -52069,9 +52081,9 @@
         <v>7.48</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>985</v>
+        <v>992</v>
       </c>
       <c r="B5" s="8">
         <v>4.7350000000000012</v>
@@ -52083,9 +52095,9 @@
         <v>6.7070000000000007</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B6" s="5">
         <v>2.8</v>
@@ -52096,10 +52108,13 @@
       <c r="D6" s="6">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B7" s="3">
         <v>4.7</v>
@@ -52109,6 +52124,9 @@
       </c>
       <c r="D7" s="4">
         <v>3.4</v>
+      </c>
+      <c r="E7" t="s">
+        <v>987</v>
       </c>
     </row>
     <row r="28" spans="6:6" x14ac:dyDescent="0.3">
